--- a/py_solution/result2.xlsx
+++ b/py_solution/result2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="问题4" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="问题4结果" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,62 +424,62 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>航向角rad</t>
+          <t>航向角(rad)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>航向角°</t>
+          <t>航向角(°)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>速度m/s</t>
+          <t>飞行速度(m/s)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>投放时间s</t>
+          <t>投放时间(s)</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>延时s</t>
+          <t>起爆延时(s)</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>投放X</t>
+          <t>投放点X</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>投放Y</t>
+          <t>投放点Y</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>投放Z</t>
+          <t>投放点Z</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>起爆X</t>
+          <t>起爆点X</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>起爆Y</t>
+          <t>起爆点Y</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>起爆Z</t>
+          <t>起爆点Z</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>总时长s</t>
+          <t>总有效遮蔽时长(s)</t>
         </is>
       </c>
     </row>
@@ -490,40 +490,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.129141</v>
+        <v>3.122525</v>
       </c>
       <c r="C2" t="n">
-        <v>179.2866</v>
+        <v>178.9075</v>
       </c>
       <c r="D2" t="n">
-        <v>120</v>
+        <v>109.32</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7275</v>
+        <v>0.4182</v>
       </c>
       <c r="F2" t="n">
-        <v>3.8212</v>
+        <v>3.3699</v>
       </c>
       <c r="G2" t="n">
-        <v>17712.71</v>
+        <v>17754.3</v>
       </c>
       <c r="H2" t="n">
-        <v>1.09</v>
+        <v>0.87</v>
       </c>
       <c r="I2" t="n">
         <v>1800</v>
       </c>
       <c r="J2" t="n">
-        <v>17254.21</v>
+        <v>17385.98</v>
       </c>
       <c r="K2" t="n">
-        <v>6.8</v>
+        <v>7.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1728.45</v>
+        <v>1744.36</v>
       </c>
       <c r="M2" t="n">
-        <v>8.305</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="3">
@@ -533,37 +533,77 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-2.068569</v>
+        <v>-2.38969</v>
       </c>
       <c r="C3" t="n">
-        <v>-118.5203</v>
+        <v>-136.9192</v>
       </c>
       <c r="D3" t="n">
-        <v>120</v>
+        <v>108.39</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5964</v>
+        <v>9.9453</v>
       </c>
       <c r="F3" t="n">
-        <v>7.2416</v>
+        <v>8.3154</v>
       </c>
       <c r="G3" t="n">
-        <v>11679.35</v>
+        <v>11212.67</v>
       </c>
       <c r="H3" t="n">
-        <v>809.9299999999999</v>
+        <v>663.72</v>
       </c>
       <c r="I3" t="n">
         <v>1400</v>
       </c>
       <c r="J3" t="n">
-        <v>11264.43</v>
+        <v>10554.36</v>
       </c>
       <c r="K3" t="n">
-        <v>46.4</v>
+        <v>48.11</v>
       </c>
       <c r="L3" t="n">
-        <v>1143.04</v>
+        <v>1061.18</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FY3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.827796</v>
+      </c>
+      <c r="C4" t="n">
+        <v>162.0207</v>
+      </c>
+      <c r="D4" t="n">
+        <v>94.98</v>
+      </c>
+      <c r="E4" t="n">
+        <v>14.5528</v>
+      </c>
+      <c r="F4" t="n">
+        <v>8.4481</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4685.26</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-2573.34</v>
+      </c>
+      <c r="I4" t="n">
+        <v>700</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3922.04</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-2325.66</v>
+      </c>
+      <c r="L4" t="n">
+        <v>350.29</v>
       </c>
     </row>
   </sheetData>
